--- a/用卷/2005.xlsx
+++ b/用卷/2005.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A216D6E-EBB8-4C37-B163-DC2EF8B8842D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954E247D-37CE-4C54-B65F-46F8A72830BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,6 +511,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -525,9 +528,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -822,12 +822,12 @@
       <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -867,7 +867,7 @@
       <c r="C5" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="22"/>
+      <c r="D5" s="23"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -876,8 +876,8 @@
       <c r="B6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="23"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -971,7 +971,7 @@
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>

--- a/用卷/2005.xlsx
+++ b/用卷/2005.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954E247D-37CE-4C54-B65F-46F8A72830BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F235EEBC-B74D-41E3-9E2B-172DBA67E474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,9 +218,6 @@
     <t>文综、理综为全国1卷,其他科目为浙江卷</t>
   </si>
   <si>
-    <t>文综、理综为全国1卷,其他科目为福建卷</t>
-  </si>
-  <si>
     <t>文综、理综为全国1卷,其他科目为江西卷</t>
   </si>
   <si>
@@ -295,6 +292,10 @@
   </si>
   <si>
     <t>2005年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>文综、理综为全国1卷,其他科目为福建卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -815,7 +816,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -823,7 +824,7 @@
     </row>
     <row r="2" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -862,10 +863,10 @@
         <v>2005</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>73</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>74</v>
       </c>
       <c r="D5" s="23"/>
     </row>
@@ -874,7 +875,7 @@
         <v>2005</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="24"/>
@@ -925,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>46</v>
@@ -939,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>46</v>
@@ -1025,7 +1026,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D18" s="4"/>
     </row>
@@ -1037,7 +1038,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -1049,7 +1050,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1"/>
     </row>
@@ -1061,7 +1062,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" s="3"/>
     </row>
@@ -1073,7 +1074,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1"/>
     </row>
@@ -1085,7 +1086,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1"/>
     </row>
@@ -1135,7 +1136,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D27" s="1"/>
     </row>
@@ -1147,7 +1148,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D28" s="1"/>
     </row>
@@ -1159,7 +1160,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D29" s="5"/>
     </row>
@@ -1171,7 +1172,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D30" s="3"/>
     </row>
@@ -1183,7 +1184,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D31" s="1"/>
     </row>
@@ -1195,7 +1196,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D32" s="3"/>
     </row>
@@ -1207,7 +1208,7 @@
         <v>54</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" s="3"/>
     </row>
@@ -1219,7 +1220,7 @@
         <v>30</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D34" s="1"/>
     </row>
@@ -1231,7 +1232,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1"/>
     </row>
@@ -1243,7 +1244,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D36" s="3"/>
     </row>
@@ -1279,7 +1280,7 @@
         <v>18</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1290,7 +1291,7 @@
         <v>32</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
@@ -1301,7 +1302,7 @@
         <v>19</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1312,7 +1313,7 @@
         <v>9</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1323,7 +1324,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -1334,7 +1335,7 @@
         <v>9</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1345,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -1356,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -1367,7 +1368,7 @@
         <v>9</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
